--- a/tests/output_excel_bool.xlsx
+++ b/tests/output_excel_bool.xlsx
@@ -16,10 +16,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>activo</t>
+    <t>nombre</t>
   </si>
   <si>
-    <t>nombre</t>
+    <t>activo</t>
   </si>
   <si>
     <t>Ana</t>
@@ -387,19 +387,19 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" t="b">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="b">
         <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" t="b">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="b">
         <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
